--- a/data/trans_bre/IMC_inf_MED_R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Clase-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.550500944524368</v>
+        <v>3.105769308580358</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-4.400290836410201</v>
+        <v>-3.153657097960891</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.8248899650246611</v>
+        <v>1.045707239372401</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.02525876711577742</v>
+        <v>0.1718142630071595</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.2273550571274589</v>
+        <v>-0.1913369248286919</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08533389210300328</v>
+        <v>0.1133881544919162</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-11.28942861792726</v>
+        <v>-7.925189740751773</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-15.43432814956426</v>
+        <v>-12.28436006332582</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-9.048614275204258</v>
+        <v>-8.257041222836179</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.4067940698699827</v>
+        <v>-0.3594285912886268</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.6292195293342805</v>
+        <v>-0.5872765592594142</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.7061623940117367</v>
+        <v>-0.6798174466522191</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12.77688768430022</v>
+        <v>14.26027817386529</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6.928806583577568</v>
+        <v>6.628389063453757</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12.59090845689718</v>
+        <v>12.94162000385468</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.7988363535388566</v>
+        <v>1.101644478545689</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5139954546084219</v>
+        <v>0.5866941933190268</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2.880415070260396</v>
+        <v>3.228710345176165</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-7.271975491027266</v>
+        <v>-6.19897288771887</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-8.055912063827506</v>
+        <v>-6.331492900027626</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-8.215247366231216</v>
+        <v>-8.52347260982871</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2774259708076068</v>
+        <v>-0.2648162486475839</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.5408448931848976</v>
+        <v>-0.4345602513971376</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4868999425433777</v>
+        <v>-0.5129337769810569</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-18.5194585514567</v>
+        <v>-16.72168077925399</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-15.95823672939306</v>
+        <v>-13.76814185765144</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-21.0121520347715</v>
+        <v>-21.4517149045898</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.5761584662323265</v>
+        <v>-0.5947639120290593</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.8143375694890546</v>
+        <v>-0.74084238414532</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.8353450568133211</v>
+        <v>-0.8381771389287799</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4.395049658859367</v>
+        <v>4.511145741272313</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2171588374130024</v>
+        <v>1.149216281104193</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2.526813233938549</v>
+        <v>2.012445437401627</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.2372485266254913</v>
+        <v>0.2516896560106482</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1052875766397413</v>
+        <v>0.1565057823720454</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.3258212966270705</v>
+        <v>0.4925475336605243</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-10.82615939982696</v>
+        <v>-9.55276217424877</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-17.2774018089297</v>
+        <v>-15.2683102095725</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-13.24547812643127</v>
+        <v>-10.75099121871092</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.347144995093027</v>
+        <v>-0.339040066080773</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.6275776728043895</v>
+        <v>-0.5788368487888216</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5310699145467627</v>
+        <v>-0.4561439982953245</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-24.74456143622042</v>
+        <v>-20.41256310585554</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-29.43520977618975</v>
+        <v>-26.30191513730012</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-30.5409698493642</v>
+        <v>-26.95929055387979</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.6381819590672467</v>
+        <v>-0.6014931616841606</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.868509349734057</v>
+        <v>-0.8100336683755606</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.8898076148070707</v>
+        <v>-0.8480119905901381</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2.219026904315423</v>
+        <v>2.795194310313324</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-4.5777870971387</v>
+        <v>-3.483663605015695</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5.596962402624996</v>
+        <v>7.932932313041842</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1060072497477076</v>
+        <v>0.1243791804277032</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1855388580129509</v>
+        <v>-0.1418705149604585</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4737992757789815</v>
+        <v>0.7797403456511107</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-5.58293375055805</v>
+        <v>-4.979301977883832</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-5.528213554683798</v>
+        <v>-6.775340645747313</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-10.40847481189213</v>
+        <v>-9.499430604349863</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1932929590684955</v>
+        <v>-0.1847523887417484</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2611239095496977</v>
+        <v>-0.3298783900299558</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.4922746823380226</v>
+        <v>-0.4761867300717691</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-14.14371349665985</v>
+        <v>-12.41566860508718</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-13.52004845537007</v>
+        <v>-13.32453743413982</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-20.84819511867072</v>
+        <v>-19.50585238181956</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.4385867885802057</v>
+        <v>-0.4026727518582419</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5152125310572506</v>
+        <v>-0.5640881622106557</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.7348982267356602</v>
+        <v>-0.7416324912932232</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2.893791622902398</v>
+        <v>2.330497302403682</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.391321872899798</v>
+        <v>-0.5770080411732456</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-1.306393621708426</v>
+        <v>-0.02302293578412179</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.1207230006320085</v>
+        <v>0.0997241589522132</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.1136688969133223</v>
+        <v>-0.03515051183704599</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01675795641932166</v>
+        <v>0.02494826233420355</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-7.750839066243293</v>
+        <v>-6.333832211796386</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-7.652041950022031</v>
+        <v>-6.697337167281728</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-5.638414247966423</v>
+        <v>-2.856871219438359</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.2589542335205361</v>
+        <v>-0.2189920991635663</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.3382582492944065</v>
+        <v>-0.3353895907552966</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.2077708689329243</v>
+        <v>-0.1116517754027616</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-17.53048358705552</v>
+        <v>-15.75980519030133</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-16.82409115644487</v>
+        <v>-14.49958869714508</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-19.12315571495115</v>
+        <v>-16.2040085183842</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.5005568038969705</v>
+        <v>-0.4690620130023347</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.6007658839944744</v>
+        <v>-0.5962522106364559</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.6032759616026496</v>
+        <v>-0.532501041527677</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1.933632254311609</v>
+        <v>2.802529347427253</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.8459747322658652</v>
+        <v>0.570495072522887</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>11.37103934884686</v>
+        <v>12.24232441006695</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.07519737727727954</v>
+        <v>0.1274219788794526</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.07396801949804846</v>
+        <v>0.05084611518599855</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.5948599616870366</v>
+        <v>0.6883361479973648</v>
       </c>
     </row>
     <row r="19">
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-2.729311294969744</v>
+        <v>2.039457576645365</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>-6.495009793247425</v>
+        <v>-8.348891920607313</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>-9.537442262411707</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.0876978424288974</v>
+        <v>0.07316861267891402</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2798737845935079</v>
+        <v>-0.3570234489689206</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>-0.5371620420380228</v>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-16.28787499972448</v>
+        <v>-11.60496325451686</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>-20.15361132992425</v>
+        <v>-20.07733416506936</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>-24.7697483944976</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.4420949288358804</v>
+        <v>-0.3695990201382323</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.7056710527631287</v>
+        <v>-0.6966601758337351</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>-0.9359416213721403</v>
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>13.54386811671871</v>
+        <v>15.76253525702043</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7.115116514265991</v>
+        <v>3.346299919606271</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>5.186167272293696</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.6215534460356564</v>
+        <v>0.6940429493312193</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4490022512278408</v>
+        <v>0.2162124266386062</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>1.171394972761657</v>
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-6.096866839030088</v>
+        <v>-4.519102527732111</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-7.472794546446582</v>
+        <v>-7.22249506972201</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-7.788989590621144</v>
+        <v>-6.822182267592307</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.2144701158235338</v>
+        <v>-0.1732814151312976</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.3537475214555721</v>
+        <v>-0.3638566551775138</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.3998279616755632</v>
+        <v>-0.3649068212032519</v>
       </c>
     </row>
     <row r="23">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-10.72038426726832</v>
+        <v>-8.569668907524324</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-11.4512474895821</v>
+        <v>-10.79468698438356</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-13.12447844956213</v>
+        <v>-11.95220132744032</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-0.3546780455312338</v>
+        <v>-0.3085242915318673</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.4955796213738137</v>
+        <v>-0.4934031973852892</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.579829608720913</v>
+        <v>-0.5551320259336073</v>
       </c>
     </row>
     <row r="24">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-1.606320458102862</v>
+        <v>-0.1737359801142862</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-3.616240905377316</v>
+        <v>-3.776973653402107</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-2.384889437775208</v>
+        <v>-1.595092209018204</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.06162158161099448</v>
+        <v>-0.005597568683679249</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-0.189962213365505</v>
+        <v>-0.2051415725022382</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-0.1382752560554462</v>
+        <v>-0.09886312695022828</v>
       </c>
     </row>
     <row r="25">
